--- a/StructureDefinition-npr-episode-identifier.xlsx
+++ b/StructureDefinition-npr-episode-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:35:49+00:00</t>
+    <t>2026-03-10T12:49:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-npr-episode-identifier.xlsx
+++ b/StructureDefinition-npr-episode-identifier.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.7</t>
+    <t>1.0.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T12:49:22+00:00</t>
+    <t>2026-03-10T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-npr-episode-identifier.xlsx
+++ b/StructureDefinition-npr-episode-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T15:33:20+00:00</t>
+    <t>2026-03-18T15:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Entydig identifikator for episode, brukt ved rapportering til NPR. Kan inneholde både string-basert og UUID-basert identifikator.</t>
+    <t>Entydig identifikator for episode som skal sendes til LMDI. Extensionen kan bære både string-basert og UUID-basert representasjon av den valgte NPR-identifikatoren. Forretningsregelen for LMDI er at kun én NPR-identifikator skal sendes per episode. Selv om helseinstitusjonens systemer kan ha flere NPR-identifiere for samme episode lokalt, skal kun én velges ved innsending - gjerne den første eller foretrukne identifikatoren lokalt.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -338,10 +338,10 @@
     <t>Y</t>
   </si>
   <si>
-    <t>String-basert NPR episode identifikator</t>
-  </si>
-  <si>
-    <t>String-basert identifikator for episoden som brukes ved rapportering til NPR.</t>
+    <t>String-representasjon av NPR episodeidentifikatoren</t>
+  </si>
+  <si>
+    <t>String-representasjon av den valgte NPR episodeidentifikatoren som sendes til LMDI. Skal oppgis dersom stringrepresentasjonen av identifikatoren er tilgjengelig.</t>
   </si>
   <si>
     <t>Extension.extension:stringIdentifier.id</t>
@@ -409,10 +409,10 @@
     <t>uuidIdentifier</t>
   </si>
   <si>
-    <t>UUID-basert NPR episode identifikator</t>
-  </si>
-  <si>
-    <t>UUID-basert identifikator for episoden som brukes ved rapportering til NPR.</t>
+    <t>UUID-representasjon av NPR episodeidentifikatoren</t>
+  </si>
+  <si>
+    <t>UUID-representasjon av den valgte NPR episodeidentifikatoren som sendes til LMDI. Skal oppgis dersom UUID-representasjonen av identifikatoren er tilgjengelig.</t>
   </si>
   <si>
     <t>Extension.extension:uuidIdentifier.id</t>

--- a/StructureDefinition-npr-episode-identifier.xlsx
+++ b/StructureDefinition-npr-episode-identifier.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T15:02:12+00:00</t>
+    <t>2026-04-21T11:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Entydig identifikator for episode som skal sendes til LMDI. Extensionen kan bære både string-basert og UUID-basert representasjon av den valgte NPR-identifikatoren. Forretningsregelen for LMDI er at kun én NPR-identifikator skal sendes per episode. Selv om helseinstitusjonens systemer kan ha flere NPR-identifiere for samme episode lokalt, skal kun én velges ved innsending - gjerne den første eller foretrukne identifikatoren lokalt.</t>
+    <t>Unik identifikator for episoden, som brukt i rapportering til Norsk pasientregister (NPR). Extensionen kan bære både string-basert og UUID-basert representasjon av den valgte NPR-identifikatoren. Hvis det er registrert flere NPR-identifiere for samme episode lokalt, skal kun én NPR-identifikator angis ved innsending til Legemiddelregisteret (LMR). Velg enten den første eller den lokalt foretrukne identifikatoren.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -341,7 +341,7 @@
     <t>String-representasjon av NPR episodeidentifikatoren</t>
   </si>
   <si>
-    <t>String-representasjon av den valgte NPR episodeidentifikatoren som sendes til LMDI. Skal oppgis dersom stringrepresentasjonen av identifikatoren er tilgjengelig.</t>
+    <t>String-representasjon av den valgte NPR episodeidentifikatoren. Skal oppgis dersom string-representasjonen av identifikatoren er tilgjengelig.</t>
   </si>
   <si>
     <t>Extension.extension:stringIdentifier.id</t>
@@ -412,7 +412,7 @@
     <t>UUID-representasjon av NPR episodeidentifikatoren</t>
   </si>
   <si>
-    <t>UUID-representasjon av den valgte NPR episodeidentifikatoren som sendes til LMDI. Skal oppgis dersom UUID-representasjonen av identifikatoren er tilgjengelig.</t>
+    <t>UUID-representasjon av den valgte NPR episodeidentifikatoren. Skal oppgis dersom UUID-representasjonen av identifikatoren er tilgjengelig.</t>
   </si>
   <si>
     <t>Extension.extension:uuidIdentifier.id</t>

--- a/StructureDefinition-npr-episode-identifier.xlsx
+++ b/StructureDefinition-npr-episode-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T07:26:56+00:00</t>
+    <t>2026-05-11T08:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-npr-episode-identifier.xlsx
+++ b/StructureDefinition-npr-episode-identifier.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T08:19:23+00:00</t>
+    <t>2026-05-31T19:08:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-npr-episode-identifier.xlsx
+++ b/StructureDefinition-npr-episode-identifier.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-31T19:08:08+00:00</t>
+    <t>2026-06-12T10:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Unik identifikator for episoden, som brukt i rapportering til Norsk pasientregister (NPR). Extensionen kan bære både string-basert og UUID-basert representasjon av den valgte NPR-identifikatoren. Hvis det er registrert flere NPR-identifiere for samme episode lokalt, skal kun én NPR-identifikator angis ved innsending til Legemiddelregisteret (LMR). Velg enten den første eller den lokalt foretrukne identifikatoren.</t>
+    <t>Unik identifikator for episoden, som brukt i rapportering til Norsk pasientregister (NPR). Extensionen kan bære både string-basert og UUID-basert representasjon av NPR-identifikatoren.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -341,7 +341,7 @@
     <t>String-representasjon av NPR episodeidentifikatoren</t>
   </si>
   <si>
-    <t>String-representasjon av den valgte NPR episodeidentifikatoren. Skal oppgis dersom string-representasjonen av identifikatoren er tilgjengelig.</t>
+    <t>String-representasjon av NPR episodeidentifikatoren. Skal oppgis dersom string-representasjonen av identifikatoren er tilgjengelig.</t>
   </si>
   <si>
     <t>Extension.extension:stringIdentifier.id</t>
@@ -412,7 +412,7 @@
     <t>UUID-representasjon av NPR episodeidentifikatoren</t>
   </si>
   <si>
-    <t>UUID-representasjon av den valgte NPR episodeidentifikatoren. Skal oppgis dersom UUID-representasjonen av identifikatoren er tilgjengelig.</t>
+    <t>UUID-representasjon av NPR episodeidentifikatoren. Skal oppgis dersom UUID-representasjonen av identifikatoren er tilgjengelig.</t>
   </si>
   <si>
     <t>Extension.extension:uuidIdentifier.id</t>

--- a/StructureDefinition-npr-episode-identifier.xlsx
+++ b/StructureDefinition-npr-episode-identifier.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T10:49:58+00:00</t>
+    <t>2026-08-24T07:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
